--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,54 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>201160</v>
+        <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>107580</v>
+        <v>87563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>630</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brun ögontröst</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Euphrasia salisburgensis subsp. schoenicola</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(B. Pett. ex Yeo) Karlsson</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fröjel,, Gtl</t>
+          <t>Lokal, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>695621</v>
+        <v>695647</v>
       </c>
       <c r="R2" t="n">
-        <v>6356315</v>
+        <v>6356609</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-09-14</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-09-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>8   Enbart 1 ex blommande, svårsedda</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,33 +771,28 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Källmyr, nu torr</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/201160</t>
+          <t>https://artportalen.se/Sighting/137222679</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105018210</v>
+        <v>201160</v>
       </c>
       <c r="B3" t="n">
         <v>107580</v>
@@ -841,17 +832,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Puser 1:26 IV, sydvästligaste delen, Gtl</t>
+          <t>Fröjel,, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695616</v>
+        <v>695621</v>
       </c>
       <c r="R3" t="n">
-        <v>6356319</v>
+        <v>6356315</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +876,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enbart 1 ex blommande, svårsedd - xkoord = 1647195, ykoord = 6356196</t>
+          <t>8   Enbart 1 ex blommande, svårsedda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,14 +904,4179 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/201160</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105018210</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107580</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>630</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brun ögontröst</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Euphrasia salisburgensis subsp. schoenicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(B. Pett. ex Yeo) Karlsson</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Puser 1:26 IV, sydvästligaste delen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>695616</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6356319</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-09-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-09-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enbart 1 ex blommande, svårsedd - xkoord = 1647195, ykoord = 6356196</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Källmyr, nu torr</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105018210</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137222682</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91911</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>695644</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6356576</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222682</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137222646</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>695811</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6356538</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222646</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137222676</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91563</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>695643</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6356624</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222676</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137222700</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87528</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>695686</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6356464</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222700</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137222729</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87528</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>695811</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6356419</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222729</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137222651</v>
+      </c>
+      <c r="B10" t="n">
+        <v>87504</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>695751</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6356553</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222651</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137222659</v>
+      </c>
+      <c r="B11" t="n">
+        <v>87504</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>695760</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6356609</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222659</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137222687</v>
+      </c>
+      <c r="B12" t="n">
+        <v>87504</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>695660</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6356564</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222687</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137222723</v>
+      </c>
+      <c r="B13" t="n">
+        <v>87504</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>695765</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6356382</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222723</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137222705</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87365</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>695634</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6356450</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222705</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137222668</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93100</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>695670</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6356676</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222668</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137222654</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90867</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>695722</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6356572</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222654</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137222726</v>
+      </c>
+      <c r="B17" t="n">
+        <v>87564</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>695802</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6356403</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222726</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137222644</v>
+      </c>
+      <c r="B18" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>695882</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6356530</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222644</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137222657</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>695751</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6356598</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222657</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137222663</v>
+      </c>
+      <c r="B20" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>695747</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6356615</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222663</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137222665</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>695713</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6356648</v>
+      </c>
+      <c r="S21" t="n">
+        <v>12</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222665</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137222670</v>
+      </c>
+      <c r="B22" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>695652</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6356676</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222670</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137222673</v>
+      </c>
+      <c r="B23" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>695614</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6356690</v>
+      </c>
+      <c r="S23" t="n">
+        <v>8</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222673</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137222677</v>
+      </c>
+      <c r="B24" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>695642</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6356615</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222677</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137222689</v>
+      </c>
+      <c r="B25" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>695678</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6356522</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222689</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137222702</v>
+      </c>
+      <c r="B26" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>695678</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6356462</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222702</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137222707</v>
+      </c>
+      <c r="B27" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>695626</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6356443</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222707</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137222710</v>
+      </c>
+      <c r="B28" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>695607</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6356402</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222710</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137222650</v>
+      </c>
+      <c r="B29" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>695750</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6356549</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222650</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137222660</v>
+      </c>
+      <c r="B30" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>695767</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6356600</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222660</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137222669</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>695664</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6356674</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222669</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137222672</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>695649</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6356674</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222672</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137222681</v>
+      </c>
+      <c r="B33" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>695640</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6356592</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222681</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137222697</v>
+      </c>
+      <c r="B34" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>695656</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6356486</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222697</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137222699</v>
+      </c>
+      <c r="B35" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>695691</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6356470</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222699</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137222701</v>
+      </c>
+      <c r="B36" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>695691</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6356461</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222701</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137222704</v>
+      </c>
+      <c r="B37" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>695642</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6356439</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222704</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137222709</v>
+      </c>
+      <c r="B38" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>695617</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6356405</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222709</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137222724</v>
+      </c>
+      <c r="B39" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>695771</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6356386</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222724</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137222736</v>
+      </c>
+      <c r="B40" t="n">
+        <v>87541</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lokal, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>695903</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6356500</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hemse</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137222736</t>
         </is>
       </c>
     </row>
@@ -928,6 +5084,43 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87563</v>
+        <v>87576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91911</v>
+        <v>91924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91563</v>
+        <v>91576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87528</v>
+        <v>87541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87528</v>
+        <v>87541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90867</v>
+        <v>90880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87564</v>
+        <v>87577</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87576</v>
+        <v>87578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91924</v>
+        <v>91926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91576</v>
+        <v>91578</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87541</v>
+        <v>87543</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87541</v>
+        <v>87543</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90880</v>
+        <v>90882</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87577</v>
+        <v>87579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87578</v>
+        <v>87581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91926</v>
+        <v>91929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91578</v>
+        <v>91581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87543</v>
+        <v>87546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87543</v>
+        <v>87546</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90882</v>
+        <v>90885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87581</v>
+        <v>87591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91929</v>
+        <v>91939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91581</v>
+        <v>91591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87546</v>
+        <v>87556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87546</v>
+        <v>87556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90885</v>
+        <v>90895</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87591</v>
+        <v>87592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91939</v>
+        <v>91940</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87556</v>
+        <v>87557</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87556</v>
+        <v>87557</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90895</v>
+        <v>90896</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87592</v>
+        <v>87595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91592</v>
+        <v>91595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87557</v>
+        <v>87560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87557</v>
+        <v>87560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90896</v>
+        <v>90899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91943</v>
+        <v>91945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91595</v>
+        <v>91597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87595</v>
+        <v>87600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91945</v>
+        <v>91950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91597</v>
+        <v>91602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87560</v>
+        <v>87565</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87560</v>
+        <v>87565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90899</v>
+        <v>90904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87600</v>
+        <v>87611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91950</v>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91602</v>
+        <v>91614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87565</v>
+        <v>87576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87565</v>
+        <v>87576</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90904</v>
+        <v>90915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87611</v>
+        <v>87612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91614</v>
+        <v>91615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87576</v>
+        <v>87577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87576</v>
+        <v>87577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90915</v>
+        <v>90916</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87612</v>
+        <v>87615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91963</v>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91615</v>
+        <v>91618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87577</v>
+        <v>87580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87577</v>
+        <v>87580</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90916</v>
+        <v>90919</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 34809-2024 artfynd.xlsx
+++ b/artfynd/A 34809-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137222679</v>
       </c>
       <c r="B2" t="n">
-        <v>87615</v>
+        <v>87619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>137222682</v>
       </c>
       <c r="B5" t="n">
-        <v>91966</v>
+        <v>91970</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>137222646</v>
       </c>
       <c r="B6" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>137222676</v>
       </c>
       <c r="B7" t="n">
-        <v>91618</v>
+        <v>91622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>137222700</v>
       </c>
       <c r="B8" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>137222729</v>
       </c>
       <c r="B9" t="n">
-        <v>87580</v>
+        <v>87584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137222651</v>
       </c>
       <c r="B10" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>137222659</v>
       </c>
       <c r="B11" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>137222687</v>
       </c>
       <c r="B12" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>137222723</v>
       </c>
       <c r="B13" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>137222705</v>
       </c>
       <c r="B14" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137222668</v>
       </c>
       <c r="B15" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>137222654</v>
       </c>
       <c r="B16" t="n">
-        <v>90919</v>
+        <v>90923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137222726</v>
       </c>
       <c r="B17" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>137222644</v>
       </c>
       <c r="B18" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>137222657</v>
       </c>
       <c r="B19" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137222663</v>
       </c>
       <c r="B20" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137222665</v>
       </c>
       <c r="B21" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137222670</v>
       </c>
       <c r="B22" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137222673</v>
       </c>
       <c r="B23" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         <v>137222677</v>
       </c>
       <c r="B24" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>137222689</v>
       </c>
       <c r="B25" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>137222702</v>
       </c>
       <c r="B26" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>137222707</v>
       </c>
       <c r="B27" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>137222710</v>
       </c>
       <c r="B28" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>137222650</v>
       </c>
       <c r="B29" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>137222660</v>
       </c>
       <c r="B30" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137222669</v>
       </c>
       <c r="B31" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>137222672</v>
       </c>
       <c r="B32" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>137222681</v>
       </c>
       <c r="B33" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>137222697</v>
       </c>
       <c r="B34" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>137222699</v>
       </c>
       <c r="B35" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         <v>137222701</v>
       </c>
       <c r="B36" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>137222704</v>
       </c>
       <c r="B37" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>137222709</v>
       </c>
       <c r="B38" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>137222724</v>
       </c>
       <c r="B39" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>137222736</v>
       </c>
       <c r="B40" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
